--- a/task2_retrieval_evaluation_v0.7.xlsx
+++ b/task2_retrieval_evaluation_v0.7.xlsx
@@ -455,7 +455,7 @@
       </c>
       <c r="E2" s="19" t="inlineStr">
         <is>
-          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
         </is>
       </c>
       <c r="F2" s="15" t="inlineStr">
@@ -487,7 +487,7 @@
       </c>
       <c r="E3" s="19" t="inlineStr">
         <is>
-          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+          <t>CASE_007; CASE_008; CASE_010</t>
         </is>
       </c>
       <c r="F3" s="15" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="E4" s="19" t="inlineStr">
         <is>
-          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+          <t>CASE_001; CASE_002; CASE_003</t>
         </is>
       </c>
       <c r="F4" s="15" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="E5" s="19" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
         </is>
       </c>
       <c r="F5" s="15" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="E19" s="19" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
         </is>
       </c>
       <c r="F19" s="15" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E20" s="19" t="inlineStr">
         <is>
-          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
         </is>
       </c>
       <c r="F20" s="15" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="E25" s="19" t="inlineStr">
         <is>
-          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
         </is>
       </c>
       <c r="F25" s="15" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
@@ -1659,7 +1659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1937,6 +1937,226 @@
       </c>
       <c r="E12" s="15" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gold reverted: Task 5 cases held out of the RAG corpus (2026-10-14)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Task 5 是评测基准（答案键），已从 RAG 语料中摘出；依赖案例的 8 道题 gold 回退到 Task 1 证据。</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>docs/evaluation.md — Task 5 定位为 end-to-end evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>question_id</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>old_expected_evidence_ids</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>new_expected_evidence_ids</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>revision criterion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RELOC_001; RELOC_002; RELOC_006; CASE_004; CASE_005; CASE_006; CASE_008</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CASE_004; CASE_005; CASE_006; CASE_008</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RELOC_004; RETURN_001; PLUS1_004; CASE_007; CASE_008; CASE_010</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CASE_007; CASE_008; CASE_010</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q003</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CASE_001; RETURN_001; RETURN_002; RETURN_003; RETURN_004</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_002; CASE_003</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q004</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008; RELOC_003; RELOC_004; RELOC_005; RELOC_006</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; CASE_008</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q018</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003; RELOC_001; RELOC_003; RELOC_006; RETURN_001</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_002; CASE_003; CASE_008; TRD_003</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q019</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001; PLUS1_001; PLUS1_002; RELOC_001</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CASE_001; CASE_004; CASE_005; CASE_006; CASE_008; KPMG_001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q024</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002; RELOC_004; RELOC_006</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CASE_007; CASE_008; CASE_010; CSIS_001; WH_001; WH_002</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q030</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001; RELOC_001; RELOC_004; RELOC_006</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CASE_004; CASE_005; CASE_006; CASE_007; WH_002; CASE_010; TRD_001</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>回退为 Task 1 证据（案例已 held-out，不可检索）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/task2_retrieval_evaluation_v0.7.xlsx
+++ b/task2_retrieval_evaluation_v0.7.xlsx
@@ -389,7 +389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1387,6 +1387,326 @@
         </is>
       </c>
       <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>我们在评估把电池与整车产能分散到中国以外，是否真能降低关税与物流成本。特斯拉最新年报对其全球制造布局与关税影响的原始披露说明了什么？</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>如果管理层要评估美国对华出口管制与关税升级对整车企业采购端的直接影响，蔚来、小鹏、理想三家在美股年报中分别披露了哪些制造基地，以及哪些与出口管制/关税相关的供应链风险？</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>export_control</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>我们要评估锂盐供应在贸易政策变化下的脆弱性。雅保（Albemarle）最新年报如何披露其锂资源与转化加工的全球布局，以及相关的贸易政策风险？</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Company Intelligence</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>假设我们把电池包组装放在墨西哥、电芯仍从中国采购，要享受USMCA优惠关税必须满足什么原产地成分门槛？</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>trade_policy</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>我们准备在印度本地建厂以服务当地市场，印度当前的进口关税水平与贸易/本地化政策基线是什么？</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>印尼对镍与电池产业链设置了哪些本地含量和矿产下游化要求，会影响我们在当地的投资与采购安排？</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>localization_policy</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>如果产能从中国转移到越南、印尼或墨西哥，物流与通关效率会带来多大额外成本？有没有可量化的基准？</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>logistics</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>电池材料出口到美国时，哪些强迫劳动合规要求会直接限制我们的供应商选择？</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>labor</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>全球动力电池供给的集中度到底有多高？有没有最新数据说明中国供应商的份额？</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Supply Chain Risk</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>董事会要在「保留中国产能」「迁往墨西哥」「迁往印尼」之间取舍，现有证据分别能支撑哪些关键判断（原产地门槛、本地含量要求、物流成本）？</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Scenario Simulation Support</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>supply_chain</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -1500,7 +1820,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>30 realistic enterprise decision questions grounded only in v0.7 Task 1 evidence IDs.</t>
+          <t>40 realistic enterprise decision questions grounded in Task 1 evidence IDs (30 written against v0.7/v0.8; Q031-Q040 added in v0.9 to make the new company-filing / WTO / logistics / labour evidence measurable).</t>
         </is>
       </c>
     </row>
@@ -1512,7 +1832,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Company Intelligence 5; Policy / Trade Risk 10; Supply Chain Risk 5; Market Access 5; Scenario Simulation Support 5.</t>
+          <t>Company Intelligence 8; Policy / Trade Risk 12; Supply Chain Risk 7; Market Access 7; Scenario Simulation Support 6.</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2477,199 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v0.9 question set extension (Q031-Q040)</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Task 1 v0.9 新增 13 条证据（公司披露 5 / WTO 3 / USMCA 1 / 世行 LPI 1 / DHS UFLPA 1 / IEA 1 / SNE 1）。新增证据若无对应题目则不可度量，因此按既有场景分类补 10 道企业决策题，gold 直接指向新增 evidence_id；原 30 题与 gold 未作改动。</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>agent proposal — pending human review</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q031</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TSLA_001</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q032</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NIO_001; XPEV_001; LI_001</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q033</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ALB_001</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q034</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>USMCA_001</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q035</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WTO_002; WTO_003</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q036</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WTO_004</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q037</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WB_001</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q038</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>DHS_001</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q039</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SNE_001; IEA_001</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q040</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>USMCA_001; WTO_004; WB_001</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/task2_retrieval_evaluation_v0.7.xlsx
+++ b/task2_retrieval_evaluation_v0.7.xlsx
@@ -389,7 +389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1707,6 +1707,102 @@
         </is>
       </c>
       <c r="F41" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>我们准备向欧盟出口 EV 电池。欧盟电池法规对进入欧盟市场的电池提出了哪些强制合规要求（碳足迹、再生材料含量、供应链尽职调查、电池护照）？</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Market Access</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>market_access</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Hard</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>欧盟对中国产纯电动车征收的最终反补贴税税率是多少？不同企业（比亚迪/吉利/上汽/特斯拉）的税率差异如何？</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>tariff</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>如果中国电池企业要在欧盟建厂或收购当地电池资产，欧盟层面的外资安全审查框架和关键原材料法案会带来哪些约束（审查范围、本土化与单一第三国依赖目标）？</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Policy / Trade Risk</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>investment_policy</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Hard</t>
         </is>
@@ -1820,7 +1916,7 @@
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>40 realistic enterprise decision questions grounded in Task 1 evidence IDs (30 written against v0.7/v0.8; Q031-Q040 added in v0.9 to make the new company-filing / WTO / logistics / labour evidence measurable).</t>
+          <t>43 realistic enterprise decision questions grounded in Task 1 evidence IDs (30 written against v0.7/v0.8; Q031-Q040 added in v0.9 for the new company-filing / WTO / logistics / labour evidence; Q041-Q043 added so the EU evidence EU_001-EU_004 is positively measurable).</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1928,7 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>Company Intelligence 8; Policy / Trade Risk 12; Supply Chain Risk 7; Market Access 7; Scenario Simulation Support 6.</t>
+          <t>Company Intelligence 8; Policy / Trade Risk 14; Supply Chain Risk 7; Market Access 8; Scenario Simulation Support 6.</t>
         </is>
       </c>
     </row>
@@ -1979,7 +2075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -2477,7 +2573,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -2667,6 +2762,80 @@
       <c r="D35" t="inlineStr">
         <is>
           <t>v0.9 新增证据的首个 gold 分配（原 30 题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EU question set extension (Q041-Q043)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>v0.8 已入库 EU_001–EU_004，但 30 道题没有任何一题的 gold 指向欧盟证据，欧盟语料只能作为噪声被扣分。补 3 道欧盟题：电池法规合规（EU_001）、对华纯电反补贴税（EU_003）、对欧投资约束（EU_002 CRMA + EU_004 外资审查）。gold 由题面信息需求决定，非按检索输出反推。</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>agent proposal — pending human review</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q041</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EU_001</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>v0.9 EU 题面扩展（原题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q042</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>EU_003</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>v0.9 EU 题面扩展（原题未改动）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q043</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>EU_002; EU_004</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>v0.9 EU 题面扩展（原题未改动）</t>
         </is>
       </c>
     </row>
